--- a/templates/PRAP_SourceData_Template_v1.6.xlsx
+++ b/templates/PRAP_SourceData_Template_v1.6.xlsx
@@ -2300,12 +2300,12 @@
           <t>PRJ-001</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Start-up</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="8" t="n">
